--- a/data_extactor/batch_10_fa/batch_0012_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0012_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allscripts Professional EHR | Allscripts Sunrise | Amkai AmkaiCharts | Apache Hadoop | Bizmatics PrognoCIS EMR | Cerner Millennium | Cerner PowerChart | ChartWare EMR | ابزارهای مهندسی نرم‌افزار به کمک کامپیوتر CASE | نرم‌افزار ورود دستورات پزشک به صورت کامپیوتری CPOE | نرم‌افزار ESRI ArcGIS | نرم‌افزار ثبت الکترونیکی تجویز دارو eMAR | Epic Systems | GE Healthcare Centricity EMR | سیستم مدیریت مراقبت‌های بهداشتی | IBM SPSS Statistics | JavaScript | LAMP Stack | سیستم مدیریت یادگیری LMS | MEDITECH Healthcare Information System HCIS | نرم‌افزار MEDITECH | McKesson ANSOS One-Staff | Mediware ClosedLoop Clinical Systems | Mediware Information Systems MediCOE | Medscribbler Enterprise | MicroFour PracticeStudio.NET EMR | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Netsmart Technologies CareNet | NextGen Healthcare Information Systems EMR | Perl | Picis CareSuite | Python | Qlik Tech QlikView | نرم‌افزار Qlik | R | SAP BusinessObjects Crystal Reports | SAS | SOAPware EMR | نرم‌افزار Salesforce | Seimens Healthineers | ابزارهای توسعه نرم‌افزار | Sparta Systems TrackWise | StatCom Patient Flow Logistics Enterprise Suite | زبان پرس‌و‌جوی ساختاریافته SQL | SynaMed EMR | Tableau | Texas Medical Software SpringCharts EMR | UNIX | VISICU eICU Program | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | نرم‌افزار eClinicalWorks EHR</t>
+          <t>Allscripts Professional EHR | Allscripts Sunrise | Amkai AmkaiCharts | Apache Hadoop | Bizmatics PrognoCIS EMR | Cerner Millennium | Cerner PowerChart | ChartWare EMR | ابزارهای مهندسی نرم‌افزار به کمک کامپیوتر CASE | نرم‌افزار ورود دستورات پزشک به صورت کامپیوتری CPOE | نرم‌افزار ESRI ArcGIS | نرم‌افزار ثبت الکترونیکی تجویز دارو eMAR | Epic Systems | GE Healthcare Centricity EMR | سیستم مدیریت مراقبت‌های بهداشتی | IBM SPSS Statistics | JavaScript | LAMP Stack | سیستم مدیریت یادگیری LMS | MEDITECH Healthcare Information System HCIS | نرم‌افزار MEDITECH | McKesson ANSOS One-Staff | Mediware ClosedLoop Clinical Systems | Mediware Information Systems MediCOE | Medscribbler Enterprise | MicroFour PracticeStudio.NET EMR | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Netsmart Technologies CareNet | NextGen Healthcare Information Systems EMR | Perl | Picis CareSuite | Python | Qlik Tech QlikView | نرم‌افزار Qlik | R | SAP BusinessObjects Crystal Reports | SAS | SOAPware EMR | نرم‌افزار Salesforce | Seimens Healthineers | ابزارهای توسعه نرم‌افزار | Sparta Systems TrackWise | StatCom Patient Flow Logistics Enterprise Suite | زبان پرس‌وجوی ساختاریافته SQL | SynaMed EMR | Tableau | Texas Medical Software SpringCharts EMR | UNIX | VISICU eICU Program | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | استراتژی‌های یادگیری | پایش | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | پزشکی و دندانپزشکی | آموزش و تربیت | خدمات مشتریان و پرسنل | مدیریت و سازماندهی | ریاضیات | طراحی | روانشناسی | مهندسی و فناوری | اداری | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | پزشکی و دندان‌پزشکی | آموزش و پرورش | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | طراحی | روان‌شناسی | مهندسی و فناوری | اداری | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | حساسیت به مشکلات | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | بیان کتبی | ابتکار و اصالت | درک شفاهی | روان بودن ایده‌ها | وضوح گفتار | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی</t>
+          <t>درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | بیان کتبی | اصالت | درک شفاهی | روانی ایده‌ها | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط‌های داخلی، کنترل‌شده از نظر دما | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | اهمیت دقیق بودن یا صحت بالا | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت نشسته | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی با تخصص پیشرفته | مدیران داده‌های بالینی | پرستاران متخصص بالینی | هماهنگ‌کنندگان تحقیقات بالینی | تحلیل‌گران سیستم‌های کامپیوتری | پرستاران مراقبت‌های ویژه بالینی | اپیدمیولوژیست‌ها | متخصصان آموزش سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مدرسان تخصص‌های بهداشتی، پس از متوسطه | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | متخصصان مدارک پزشکی | مدیران خدمات پزشکی و بهداشتی | پرستاران متخصص (NP) | مربیان و مدرسان پرستاری، پس از متوسطه | نمایندگان بیمار | پزشکان طب پیشگیری | پرستاران ثبت‌شده | دستیاران پژوهشی علوم اجتماعی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | تحلیلگران سیستم‌های کامپیوتری | پرستاران بخش مراقبت‌های ویژه | اپیدمیولوژیست‌ها | متخصصان آموزش بهداشت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | استادان تخصص‌های بهداشتی، پس از متوسطه | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | متخصصان مدارک پزشکی | مدیران خدمات پزشکی و بهداشتی | پرستاران متخصص | مربیان و استادان پرستاری، پس از متوسطه | نمایندگان بیمار | پزشکان طب پیشگیری | پرستاران ثبت‌شده | دستیاران تحقیقات علوم اجتماعی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3M Post-it App | AJAX | نرم‌افزار مدیریت دسترسی | AccessData FTK | نرم‌افزار اکتیو دایرکتوری | Adobe ActionScript | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | نرم‌افزار ضد تروجان | نرم‌افزار ضد فیشینگ | نرم‌افزار ضد جاسوس‌افزار | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | ArcSight Enterprise Threat and Risk Management | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | نرم‌افزار تحلیل خودکار ردپای ممیزی | نرم‌افزار نصب خودکار | نرم‌افزار ردیابی خودکار رسانه | نرم‌افزار پشتیبان‌گیری و آرشیو | Bash | Berkeley Internet Domain Name BIND | نرم‌افزار Blackboard | Blink | پروتکل مسیریابی مرزی BGP | C | C# | C++ | Check Point Next Generation Secure Web Gateway | Chef | Cisco Systems CiscoWorks | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | نرم‌افزار جرم‌یابی کامپیوتری | نرم‌افزار تست انطباق و اعتبارسنجی | نرم‌افزار مدیریت کلید رمزنگاری | سیستم کنترل اطلاعات مشتری CICS | Delphi Technology | Diameter | Django | Docker | سیستم نام دامنه DNS | Drupal | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | نرم‌افزار رمزگذاری سرتاسری | Enterprise JavaBeans | Epic Systems | Ethereal | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار فایروال | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Angular | Google Sites | Guidance Software EnCase Forensic | HP Fortify | HP WebInspect | Hewlett Packard HP-UX | هانی‌پات | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | IBM QRadar SIEM | IBM Tivoli Access Management TAM | IBM Tivoli Identity Management TIM | IBM WebSphere | ISS RealSecure | Imperva SecureSphere | نرم‌افزار محیط توسعه یکپارچه IDE | نرم‌افزار تأیید یکپارچگی | سیستم تشخیص نفوذ IDS | سیستم پیشگیری از نفوذ IPS | IpFilter | IpTables | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Juniper Networks NetScreen-Security Manager | Kali Linux | نرم‌افزار نظارت بر فشردن کلیدها | KornShell | LAMP Stack | LexisNexis | نرم‌افزار رمزگذاری لینک | Linux | نرم‌افزار MITRE ATT&amp;CK | McAfee | McAfee VirusScan | Metasploit | Micro Focus OpenView | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Hyper-V Server | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | MongoDB | MySQL | Nagios | National Instruments LabVIEW | نرم‌افزار ارزیابی آسیب‌پذیری شبکه و سیستم | نرم‌افزار خدمات دایرکتوری شبکه | سیستم‌های پیشگیری از نفوذ شبکه NIPS | نرم‌افزار ممیزی امنیت شبکه | نرم‌افزار ممیزی شبکه، سخت‌افزار و نرم‌افزار | NoSQL | Node.js | Norton AntiVirus | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Net Manager | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Solaris | Oracle WebLogic Server | PHP | Palo Alto Networks Next-Generation Security Platform | نرم‌افزار کرک پسورد | نرم‌افزار مدیریت پسورد | نرم‌افزار مدیریت وصله و به‌روزرسانی | نرم‌افزار تست نفوذ | نرم‌افزار Perforce Helix | Perl | Ping Identity | Portswigger BurP Suite | PostgreSQL | نرم‌افزار بررسی چک‌سام برنامه | Puppet | Python | Qlik Tech QlikView | Qualys Cloud Platform | Quest BigBrother | Rapid7 Nexpose | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سرویس کاربر شماره‌گیری احراز هویت از راه دور RADIUS | نرم‌افزار شناسایی روت‌کیت | Ruby | Ruby on Rails | SAP Crystal Reports | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Scala | نرم‌افزار فیلترینگ اینترنت امن | نرم‌افزار پوسته امن SSH | نرم‌افزار مدیریت حوادث امنیتی | نرم‌افزار ارزیابی ریسک امنیتی | Selenium | شل اسکریپت | نرم‌افزار مدیریت کارت هوشمند | Sniffer Investigator | Snort | Splunk Enterprise | Spring Framework | نرم‌افزار محافظت در برابر درهم‌شکستن پشته SSP | زبان پرس‌و‌جوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Blue Coat Data Loss Prevention | Symantec Endpoint Protection | نرم‌افزار بازیابی فاجعه سیستم و داده‌ها | نرم‌افزار تست سیستم | Tableau | Tcpdump | Tenable Nessus | Teradata Database | The MathWorks MATLAB | Trend Micro TippingPoint | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار اسکن ویروس | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Websense Data Loss Prevention | WinMerge | Wireshark | eMASS</t>
+          <t>3M Post-it App | AJAX | نرم‌افزار مدیریت دسترسی | AccessData FTK | نرم‌افزار اکتیو دایرکتوری | Adobe ActionScript | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | نرم‌افزار ضد تروجان | نرم‌افزار ضد فیشینگ | نرم‌افزار ضد جاسوس‌افزار | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | ArcSight Enterprise Threat and Risk Management | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | نرم‌افزار تحلیل خودکار ردپای ممیزی | نرم‌افزار نصب خودکار | نرم‌افزار ردیابی خودکار رسانه | نرم‌افزار پشتیبان‌گیری و بایگانی | Bash | Berkeley Internet Domain Name BIND | نرم‌افزار Blackboard | Blink | پروتکل مسیریابی مرزی BGP | C | C# | C++ | Check Point Next Generation Secure Web Gateway | Chef | Cisco Systems CiscoWorks | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | نرم‌افزار جرم‌یابی کامپیوتری | نرم‌افزار تست انطباق و اعتبارسنجی | نرم‌افزار مدیریت کلید رمزنگاری | سیستم کنترل اطلاعات مشتری CICS | Delphi Technology | Diameter | Django | Docker | سیستم نام دامنه DNS | Drupal | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | نرم‌افزار رمزگذاری سرتاسری | Enterprise JavaBeans | Epic Systems | Ethereal | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار فایروال | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Angular | Google Sites | Guidance Software EnCase Forensic | HP Fortify | HP WebInspect | Hewlett Packard HP-UX | هانی‌پات | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | IBM QRadar SIEM | IBM Tivoli Access Management TAM | IBM Tivoli Identity Management TIM | IBM WebSphere | ISS RealSecure | Imperva SecureSphere | نرم‌افزار محیط توسعه یکپارچه IDE | نرم‌افزار تأیید یکپارچگی | سیستم تشخیص نفوذ IDS | سیستم پیشگیری از نفوذ IPS | IpFilter | IpTables | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Juniper Networks NetScreen-Security Manager | Kali Linux | نرم‌افزار نظارت بر فشردن کلیدها | KornShell | LAMP Stack | LexisNexis | نرم‌افزار رمزگذاری لینک | Linux | نرم‌افزار MITRE ATT&amp;CK | McAfee | McAfee VirusScan | Metasploit | Micro Focus OpenView | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Hyper-V Server | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | MongoDB | MySQL | Nagios | National Instruments LabVIEW | نرم‌افزار ارزیابی آسیب‌پذیری شبکه و سیستم | نرم‌افزار خدمات دایرکتوری شبکه | سیستم‌های پیشگیری از نفوذ شبکه NIPS | نرم‌افزار ممیزی امنیت شبکه | نرم‌افزار ممیزی شبکه، سخت‌افزار و نرم‌افزار | NoSQL | Node.js | Norton AntiVirus | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Net Manager | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Solaris | Oracle WebLogic Server | PHP | Palo Alto Networks Next-Generation Security Platform | نرم‌افزار کرک پسورد | نرم‌افزار مدیریت پسورد | نرم‌افزار مدیریت وصله و به‌روزرسانی | نرم‌افزار تست نفوذ | نرم‌افزار Perforce Helix | Perl | Ping Identity | Portswigger BurP Suite | PostgreSQL | نرم‌افزار بررسی چک‌سام برنامه | Puppet | Python | Qlik Tech QlikView | Qualys Cloud Platform | Quest BigBrother | Rapid7 Nexpose | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سرویس کاربر شماره‌گیری احراز هویت از راه دور RADIUS | نرم‌افزار شناسایی روت‌کیت | Ruby | Ruby on Rails | SAP Crystal Reports | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Scala | نرم‌افزار فیلترینگ اینترنت امن | نرم‌افزار پوسته امن SSH | نرم‌افزار مدیریت حوادث امنیتی | نرم‌افزار ارزیابی ریسک امنیتی | Selenium | Shell script | نرم‌افزار مدیریت کارت هوشمند | Sniffer Investigator | Snort | Splunk Enterprise | Spring Framework | نرم‌افزار محافظت در برابر درهم‌شکستن پشته SSP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Blue Coat Data Loss Prevention | Symantec Endpoint Protection | نرم‌افزار بازیابی فاجعه سیستم و داده‌ها | نرم‌افزار تست سیستم | Tableau | Tcpdump | Tenable Nessus | Teradata Database | The MathWorks MATLAB | Trend Micro TippingPoint | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار اسکن ویروس | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Websense Data Loss Prevention | WinMerge | Wireshark | eMASS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | پایش | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | مدیریت و سازماندهی | مخابرات | مهندسی و فناوری | خدمات مشتریان و پرسنل | امنیت و ایمنی عمومی | آموزش و تربیت</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | مدیریت و اداره | مخابرات | مهندسی و فناوری | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مشکلات | استدلال قیاسی | استدلال استقرایی | بیان کتبی | سازماندهی اطلاعات | بیان شفاهی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | ابتکار و اصالت | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | محیط‌های داخلی، کنترل‌شده از نظر دما | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | ارتباط با دیگران | صرف زمان به صورت نشسته | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق بودن یا صحت بالا | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران جرم‌یابی دیجیتال | متخصصان مدیریت اسناد | مهندسان امنیت اطلاعات | تحلیل‌گران اطلاعاتی | مدیران شبکه و سیستم‌های کامپیوتری | تست‌کنندگان نفوذ | متخصصان مدیریت امنیت | مدیران امنیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات</t>
+          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران جرم‌شناسی دیجیتال | متخصصان مدیریت اسناد | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | متخصصان مدیریت امنیت | مدیران امنیتی | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3D graphics software | Ada | نرم‌افزار محاسبات عددی پیشرفته | نرم‌افزار الگوریتمی | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Web Services AWS CloudFormation | Amazon Web Services AWS SageMaker | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Airflow | Apache Cassandra | Apache Flume | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Pig | Apache Solr | Apache Spark | Apache Subversion SVN | Augmint | نرم‌افزار تولید خودکار اسناد | Bash | Bidirectional encoder representations from transformers (BERT) | برنامه‌های نرم‌افزاری تجاری | C | C# | C++ | CMake | Charm++ | نرم‌افزار چت‌بات | Chef | Clustermatic | نرم‌افزار آمار محاسباتی | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار تصویرسازی داده‌ها | Django | Docker | Doxygen | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eiffel | Elasticsearch | Embarcadero JBuilder | زبان نشانه‌گذاری توسعه‌پذیر XML | تبدیل‌های زبان شیوه‌نامه توسعه‌پذیر XSLT | مترجم فرمول FORTRAN | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | GitLab | Go | Google Ads | Google Analytics | Grafana Labs Grafana Cloud | خطوط لوله گرافیکی | کامپایلرهای Greenhills Ada | کتابخانه‌های نرم‌افزاری با کارایی بالا | Hugging Face | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Rational Apex | IBM Rational Rose XDE | IBM SPSS Statistics | IBM Terraform | نرم‌افزار محیط توسعه یکپارچه IDE | Intel Integrated Performance Primitives | Intel Math Kernel Library | JavaScript | Jenkins CI | Jupyter Notebook | Kubernetes | LangChain | Linux | زبان پردازش لیست LISP | کامپایلرهای ماشین مجازی سطح پایین LLVM | نرم‌افزار ریاضی | MicroStrategy | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Visual Studio.NET | Microsoft Windows XP | Minitab | MongoDB | نرم‌افزار نمایش داده‌های چندحسی | MySQL | National Instruments LabVIEW | NoSQL | Node.js | نرم‌افزار محیط توسعه شیءگرا | Open Graphics Library OpenGL | OpenAI ChatGPT | نرم‌افزار بهینه‌سازی | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle Solaris | PHP | PTC Creo Parametric | نرم‌افزار سیستم‌های موازی | سیستم مدیریت پیکربندی نرم‌افزار Perforce | Perl | نرم‌افزار فایل پلاگین | کامپایلرهای موازی‌ساز Polaris | Polhemus Fasttrack System | PostgreSQL | Prolog | Prometheus | Puppet | PyTorch | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Redis | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سیستم مدیریت پایگاه داده رابطه‌ای | شبیه‌ساز رایس برای چندپردازنده‌های سطح دستورالعمل RSIM | Ruby | SAP Business Objects | SAS | Scala | Scikit-learn | شل اسکریپت | نرم‌افزار شبیه‌سازی | Snowflake | کتابخانه‌های نرم‌افزاری | نرم‌افزار مدیریت کد منبع SCM | Splunk Enterprise | StataCorp Stata | زبان پرس‌و‌جوی ساختاریافته SQL | نرم‌افزار تست سیستم | Tableau | TensorFlow | Teradata Database | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VME PowerPC VxWorks | نرم‌افزار پایگاه داده برداری | Verilog | نرم‌افزار ویرایش ویدیو | محیط وایکاتو برای تحلیل دانش Weka | pandas</t>
+          <t>نرم‌افزار گرافیک سه‌بعدی | Ada | نرم‌افزار محاسبات عددی پیشرفته | نرم‌افزار الگوریتمی | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Web Services AWS CloudFormation | Amazon Web Services AWS SageMaker | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Airflow | Apache Cassandra | Apache Flume | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Pig | Apache Solr | Apache Spark | Apache Subversion SVN | Augmint | نرم‌افزار تولید خودکار اسناد | Bash | Bidirectional encoder representations from transformers (BERT) | برنامه‌های نرم‌افزاری تجاری | C | C# | C++ | CMake | Charm++ | نرم‌افزار چت‌بات | Chef | Clustermatic | نرم‌افزار آمار محاسباتی | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار تجسم داده | Django | Docker | Doxygen | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eiffel | Elasticsearch | Embarcadero JBuilder | زبان نشانه‌گذاری توسعه‌پذیر XML | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | Formula translation/translator FORTRAN | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | GitLab | Go | Google Ads | Google Analytics | Grafana Labs Grafana Cloud | خطوط لوله گرافیکی | کامپایلرهای Greenhills Ada | کتابخانه‌های نرم‌افزاری با کارایی بالا | Hugging Face | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Rational Apex | IBM Rational Rose XDE | IBM SPSS Statistics | IBM Terraform | نرم‌افزار محیط توسعه یکپارچه IDE | Intel Integrated Performance Primitives | Intel Math Kernel Library | JavaScript | Jenkins CI | Jupyter Notebook | Kubernetes | LangChain | Linux | زبان پردازش لیست LISP | کامپایلرهای ماشین مجازی سطح پایین LLVM | نرم‌افزار ریاضی | MicroStrategy | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Visual Studio.NET | Microsoft Windows XP | Minitab | MongoDB | نرم‌افزار نمایش داده‌های چندحسی | MySQL | National Instruments LabVIEW | NoSQL | Node.js | نرم‌افزار محیط توسعه شیءگرا | کتابخانه گرافیکی باز OpenGL | OpenAI ChatGPT | نرم‌افزار بهینه‌سازی | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle Solaris | PHP | PTC Creo Parametric | نرم‌افزار سیستم‌های موازی | سیستم مدیریت پیکربندی نرم‌افزار Perforce | Perl | نرم‌افزار فایل پلاگین | کامپایلرهای موازی‌ساز Polaris | Polhemus Fasttrack System | PostgreSQL | Prolog | Prometheus | Puppet | PyTorch | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Redis | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سیستم مدیریت پایگاه داده رابطه‌ای | شبیه‌ساز رایس برای چندپردازنده‌های سطح دستورالعمل RSIM | Ruby | SAP Business Objects | SAS | Scala | Scikit-learn | Shell script | نرم‌افزار شبیه‌سازی | Snowflake | کتابخانه‌های نرم‌افزاری | نرم‌افزار مدیریت کد منبع SCM | Splunk Enterprise | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار تست سیستم | Tableau | TensorFlow | Teradata Database | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VME PowerPC VxWorks | نرم‌افزار پایگاه داده برداری | Verilog | نرم‌افزار ویرایش ویدیو | محیط وایکاتو برای تحلیل دانش Weka | pandas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | علوم تجربی | پایش | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و سازماندهی | طراحی | مخابرات</t>
+          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره | طراحی | مخابرات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | روان بودن ایده‌ها | حساسیت به مشکلات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | بیان کتبی | سازماندهی اطلاعات | ابتکار و اصالت | استدلال ریاضی | وضوح گفتار | سهولت در کار با اعداد | تجسم فضایی | تشخیص گفتار | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | روانی ایده‌ها | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | اصالت | استدلال ریاضی | وضوح گفتار | توانایی عددی | تجسم | تشخیص گفتار | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | محیط‌های داخلی، کنترل‌شده از نظر دما | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مهندسان زیستی و مهندسان پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | مدرسان علوم کامپیوتر، پس از متوسطه | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران سیستم‌های اطلاعاتی و کامپیوتری | دانشمندان داده | معماران پایگاه داده | مدیران پروژه فناوری اطلاعات | ریاضی‌دانان | تکنسین‌ها و فن‌آوران مهندسی فناوری نانو | مدیران علوم طبیعی | تحلیل‌گران تحقیق در عملیات | مهندسان رباتیک | توسعه‌دهندگان نرم‌افزار | آمارشناسان</t>
+          <t>مدیران معماری و مهندسی | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | اساتید علوم رایانه، پس از متوسطه | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | معماران پایگاه داده | مدیران پروژه فناوری اطلاعات | ریاضی‌دانان | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدیران علوم طبیعی | تحلیل‌گران تحقیق در عملیات | مهندسان رباتیک | توسعه‌دهندگان نرم‌افزار | آمارشناسان</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار ضد جاسوس‌افزار | نرم‌افزار آنتی‌ویروس | Apache Tomcat | Apple macOS | نرم‌افزار مدیریت برنامه‌ها | Arping | نرم‌افزار نصب خودکار | B&amp;W Port Scanner | BMC Software Control-M | BMC Software Remedy IT Service Management Suite | Bash | Bentley Systems ProjectWise | BitWizard B.V. mtr | BlackBerry Enterprise Server | پروتکل مسیریابی مرزی BGP | Cisco Systems Cisco NetFlow Collection Engine | Cisco Systems Cisco Traffic Analyzer | Cisco Systems CiscoWorks | Cisco Systems CiscoWorks LAN Management Solution | نرم‌افزار رایانش ابری Citrix | Clarified Networks Clarified Analyzer | Colasoft Capsa Enterprise | Colasoft Capsa Free | Compuware ClientVantage Agentless Monitoring | Congruity Technologies Inspector | نرم‌افزار اتصال | سیستم کنترل اطلاعات مشتری CICS | Dartware InterMapper | نرم‌افزار مدیریت پایگاه داده | Dig | EMC Ionix Network Configuration Manager | EMC NetWorker | EMC Symmetrix DMX | نرم‌افزار رمزگذاری | Ethereal | Ettercap NG | نرم‌افزار سرور فایل | نرم‌افزار فایروال | Fluke Networks Enterprise LANMeter | نرم‌افزار میز کمک (هلپ دسک) | Hewlett Packard HP-UX | Hewlett-Packard HP Network Node Manager | IBM AIX | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | IBM Security Network Intrusion Prevention System | IBM Tivoli NetView Distribution Manager | IBM WebSphere | سیستم پیشگیری از نفوذ IPS | زبان کنترل کار JCL | KornShell | LAMP Stack | Linux | نرم‌افزار تست بارگذاری | LogMatrix NerveCenter | McAfee | Microsoft Access | Microsoft Active Directory | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Hyper-V Server | Microsoft Internet Information Services (IIS) | Microsoft Network Monitor | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Windows PowerShell | Microsoft Windows Server | Microsoft Windows Sysprep | Microsoft Word | MySQL | NIKSUN NetDetector | Nagios | NetScout Sniffer Global Analyzer | NetScout Sniffer Portable Professional Analyzer | Network Instruments Observer Standard | نرم‌افزار ارزیابی آسیب‌پذیری شبکه و سیستم | نرم‌افزار طراحی شبکه | نرم‌افزار تشخیص نفوذ شبکه | Norton AntiVirus | نرم‌افزار امنیت سایبری NortonLifeLock | NovaStor NovaBACKUP | Novell eDirectory | Nslookup | OPNET SP Sentinel | Oracle Java | Oracle Solaris | آنالایزرهای بسته | نرم‌افزار فیلتر بسته | نرم‌افزار مدیریت وصله و به‌روزرسانی | Perl | Ping Identity | اسکنرهای پورت | نرم‌افزار برنامه‌ریزی پروژه | Python | Red Hat Enterprise Linux | نرم‌افزار کنترل از راه دور | نرم‌افزار شناسایی روت‌کیت | Route | Roxio Retrospect | Ruby | نرم‌افزار مدیریت حوادث امنیتی | ServiceNow | شل اسکریپت | SolarWinds | Sonicwall SonicOS Enhanced | Splunk Enterprise | نرم‌افزار شبکه ذخیره‌سازی SAN | زبان پرس‌و‌جوی ساختاریافته SQL | Symantec Veritas NetBackup | Symantec pcAnywhere | نرم‌افزار سیستم پشتیبان‌گیری نوار | Tcpdump | Teradata Database | Traceroute | شکل‌دهنده‌های ترافیک | UNIX | UNIX Shell | Ubuntu | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | WildPackets OmniPeek Network Analyzer | Wireshark | Zabbix | ifconfig | ipconfig | nbtstat | netstat | ngrep</t>
+          <t>Adobe Acrobat | نرم‌افزار ضد جاسوس‌افزار | نرم‌افزار آنتی‌ویروس | Apache Tomcat | Apple macOS | نرم‌افزار مدیریت برنامه‌ها | Arping | نرم‌افزار نصب خودکار | B&amp;W Port Scanner | BMC Software Control-M | BMC Software Remedy IT Service Management Suite | Bash | Bentley Systems ProjectWise | BitWizard B.V. mtr | BlackBerry Enterprise Server | پروتکل مسیریابی مرزی BGP | Cisco Systems Cisco NetFlow Collection Engine | Cisco Systems Cisco Traffic Analyzer | Cisco Systems CiscoWorks | Cisco Systems CiscoWorks LAN Management Solution | نرم‌افزار رایانش ابری Citrix | Clarified Networks Clarified Analyzer | Colasoft Capsa Enterprise | Colasoft Capsa Free | Compuware ClientVantage Agentless Monitoring | Congruity Technologies Inspector | نرم‌افزار اتصال | سیستم کنترل اطلاعات مشتری CICS | Dartware InterMapper | نرم‌افزار مدیریت پایگاه داده | Dig | EMC Ionix Network Configuration Manager | EMC NetWorker | EMC Symmetrix DMX | نرم‌افزار رمزگذاری | Ethereal | Ettercap NG | نرم‌افزار فایل سرور | نرم‌افزار فایروال | Fluke Networks Enterprise LANMeter | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett-Packard HP Network Node Manager | IBM AIX | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | IBM Security Network Intrusion Prevention System | IBM Tivoli NetView Distribution Manager | IBM WebSphere | سیستم پیشگیری از نفوذ IPS | زبان کنترل کار JCL | KornShell | LAMP Stack | Linux | نرم‌افزار تست بارگذاری | LogMatrix NerveCenter | McAfee | Microsoft Access | Microsoft Active Directory | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Hyper-V Server | Microsoft Internet Information Services (IIS) | Microsoft Network Monitor | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Windows PowerShell | Microsoft Windows Server | Microsoft Windows Sysprep | Microsoft Word | MySQL | NIKSUN NetDetector | Nagios | NetScout Sniffer Global Analyzer | NetScout Sniffer Portable Professional Analyzer | Network Instruments Observer Standard | نرم‌افزار ارزیابی آسیب‌پذیری شبکه و سیستم | نرم‌افزار طراحی شبکه | نرم‌افزار تشخیص نفوذ شبکه | Norton AntiVirus | نرم‌افزار امنیت سایبری NortonLifeLock | NovaStor NovaBACKUP | Novell eDirectory | Nslookup | OPNET SP Sentinel | Oracle Java | Oracle Solaris | آنالایزرهای بسته | نرم‌افزار فیلتر بسته | نرم‌افزار مدیریت وصله و به‌روزرسانی | Perl | Ping Identity | اسکنرهای پورت | نرم‌افزار برنامه‌ریزی پروژه | Python | Red Hat Enterprise Linux | نرم‌افزار کنترل از راه دور | نرم‌افزار شناسایی روت‌کیت | Route | Roxio Retrospect | Ruby | نرم‌افزار مدیریت حوادث امنیتی | ServiceNow | Shell script | SolarWinds | Sonicwall SonicOS Enhanced | Splunk Enterprise | نرم‌افزار شبکه ذخیره‌سازی SAN | زبان پرس‌وجوی ساختاریافته SQL | Symantec Veritas NetBackup | Symantec pcAnywhere | نرم‌افزار سیستم پشتیبان‌گیری نوار | Tcpdump | Teradata Database | Traceroute | شکل‌دهنده‌های ترافیک | UNIX | UNIX Shell | Ubuntu | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | WildPackets OmniPeek Network Analyzer | Wireshark | Zabbix | ifconfig | ipconfig | nbtstat | netstat | ngrep</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | پایش | یادگیری فعال | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مخابرات | خدمات مشتریان و پرسنل | مهندسی و فناوری | زبان انگلیسی | مدیریت و سازماندهی</t>
+          <t>رایانه و الکترونیک | مخابرات | خدمات مشتری و شخصی | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مشکلات | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | درک کتبی | سازماندهی اطلاعات | بیان کتبی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | چالاکی انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات | بیان کتبی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | مهارت انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | محیط‌های داخلی، کنترل‌شده از نظر دما | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق بودن یا صحت بالا | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت نشسته | اهمیت تکرار کارهای مشابه | نامه‌ها و یادداشت‌های کتبی | تعداد دفعات تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم</t>
+          <t>مکالمات تلفنی | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | تکنسین‌های پخش رسانه‌ای | معماران شبکه کامپیوتری | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | تکنسین‌ها و فن‌آوران مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | تست‌کنندگان نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصب‌کنندگان و تعمیرکاران تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | مدیران وب</t>
+          <t>مهندسان بلاک‌چین | تکنسین‌های پخش | معماران شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | مدیران وب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3M Post-it App | AJAX | نرم‌افزار اکتیو دایرکتوری | Adobe Acrobat | Adobe ActionScript | نرم‌افزار Adobe Creative Cloud | Adobe Distiller | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon Redshift | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Final Cut Pro | Apple iOS | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk Revit | نرم‌افزار نصب خودکار | Bash | Bentley MicroStation | نرم‌افزار Blackboard | Blink | C | C# | C++ | نرم‌افزار مرکز تماس | برگه شیوه‌نامه آبشاری CSS | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | CrossTec NetOp Remote Control | سیستم کنترل اطلاعات مشتری CICS | Dartware InterMapper | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ورود داده‌ها | نرم‌افزار پایگاه داده | نرم‌افزار ردیابی نقص | Delphi Technology | نرم‌افزار استقرار | نرم‌افزار پارتیشن‌بندی دسکتاپ | نرم‌افزار بازیابی فاجعه | Django | Docker | سیستم نام دامنه DNS | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | نرم‌افزار مدیریت عناصر | نرم‌افزار رمزگذاری | Enterprise JavaBeans | Epic Systems | نرم‌افزار نظارت بر گزارش رویدادها | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | FileMaker Pro | نرم‌افزار فایروال | Flipgrid | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Google Android | Google Angular | Google Classroom | Google Docs | Google Drive | Google Meet | Google Sites | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM WebSphere | نرم‌افزار یکپارچه‌سازی سیستم‌های اطلاعاتی | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | KornShell | LAMP Stack | LexisNexis | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Lucid IQ CMP | نرم‌افزار MEDITECH | Mac HelpMate | Marketo Marketing Automation | McAfee | نرم‌افزار مدیریت ذخیره‌سازی رسانه | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Volume Shadow Copy Service | Microsoft Windows | Microsoft Windows Pre-installation Environment | Microsoft Windows Server | Microsoft Word | نرم‌افزار مهاجرت | MongoDB | Moodle | MySQL | Nagios | National Instruments LabVIEW | Nearpod | NetSuite ERP | نرم‌افزار خدمات دایرکتوری شبکه | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | نرم‌افزار نظارت بر سیستم عامل | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | ParentSquare | نرم‌افزار مدیریت پسورد | نرم‌افزار مدیریت وصله | Perforce Helix software | Perl | نرم‌افزار عیب‌یابی کامپیوتر شخصی | Poll Everywhere | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار کنترل از راه دور | نرم‌افزار سرور نصب از راه دور | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 50 Accounting | Salesforce Visualforce | نرم‌افزار Salesforce | Schoology | Seesaw | ServiceNow | شل اسکریپت | Skype | Slack | SmugMug Flickr | نرم‌افزار مدیریت دارایی‌های نرم‌افزاری SAM | SolarWinds | Splunk Enterprise | Spring Boot | Spring Framework | Stac Software ReachOut | StataCorp Stata | زبان پرس‌و‌جوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec LiveState | Symantec Norton Utilities | Symantec pcAnywhere | Tableau | نرم‌افزار مالیاتی | Teradata Database | The MathWorks MATLAB | Transact-SQL | Trimble SketchUp Pro | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار اسکن ویروس | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Wireshark | نرم‌افزار Yardi | YouTube | Zoom | iPro | jQuery</t>
+          <t>3M Post-it App | AJAX | نرم‌افزار اکتیو دایرکتوری | Adobe Acrobat | Adobe ActionScript | نرم‌افزار Adobe Creative Cloud | Adobe Distiller | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon Redshift | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Final Cut Pro | Apple iOS | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk Revit | نرم‌افزار نصب خودکار | Bash | Bentley MicroStation | نرم‌افزار Blackboard | Blink | C | C# | C++ | نرم‌افزار مرکز تماس | برگه‌های سبک آبشاری CSS | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | CrossTec NetOp Remote Control | سیستم کنترل اطلاعات مشتری CICS | Dartware InterMapper | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار ردیابی نقص | Delphi Technology | نرم‌افزار استقرار | نرم‌افزار پارتیشن‌بندی دسکتاپ | نرم‌افزار بازیابی فاجعه | Django | Docker | سیستم نام دامنه DNS | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | نرم‌افزار مدیریت عناصر | نرم‌افزار رمزگذاری | Enterprise JavaBeans | Epic Systems | نرم‌افزار نظارت بر گزارش رویدادها | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | FileMaker Pro | نرم‌افزار فایروال | Flipgrid | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Google Android | Google Angular | Google Classroom | Google Docs | Google Drive | Google Meet | Google Sites | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM WebSphere | نرم‌افزار یکپارچه‌سازی سیستم‌های اطلاعاتی | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | KornShell | LAMP Stack | LexisNexis | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Lucid IQ CMP | نرم‌افزار MEDITECH | Mac HelpMate | Marketo Marketing Automation | McAfee | نرم‌افزار مدیریت ذخیره‌سازی رسانه | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Volume Shadow Copy Service | Microsoft Windows | Microsoft Windows Pre-installation Environment | Microsoft Windows Server | Microsoft Word | نرم‌افزار مهاجرت | MongoDB | Moodle | MySQL | Nagios | National Instruments LabVIEW | Nearpod | NetSuite ERP | نرم‌افزار خدمات دایرکتوری شبکه | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | نرم‌افزار نظارت بر سیستم عامل | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | ParentSquare | نرم‌افزار مدیریت پسورد | نرم‌افزار مدیریت وصله | نرم‌افزار Perforce Helix | Perl | نرم‌افزار عیب‌یابی کامپیوتر شخصی | Poll Everywhere | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار کنترل از راه دور | نرم‌افزار سرور نصب از راه دور | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 50 Accounting | Salesforce Visualforce | نرم‌افزار Salesforce | Schoology | Seesaw | ServiceNow | Shell script | Skype | Slack | SmugMug Flickr | نرم‌افزار مدیریت دارایی نرم‌افزار SAM | SolarWinds | Splunk Enterprise | Spring Boot | Spring Framework | Stac Software ReachOut | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec LiveState | Symantec Norton Utilities | Symantec pcAnywhere | Tableau | نرم‌افزار مالیاتی | Teradata Database | The MathWorks MATLAB | Transact-SQL | Trimble SketchUp Pro | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار اسکن ویروس | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Wireshark | نرم‌افزار Yardi | YouTube | Zoom | iPro | jQuery</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | استراتژی‌های یادگیری | پایش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | خدمات مشتریان و پرسنل | مخابرات | زبان انگلیسی | آموزش و تربیت | مکانیک | مهندسی و فناوری | مدیریت و سازماندهی | اداری | ارتباطات و رسانه | طراحی</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | زبان انگلیسی | آموزش و پرورش | مکانیک | مهندسی و فناوری | مدیریت و اداره | اداری | ارتباطات و رسانه | طراحی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | سازماندهی اطلاعات | حساسیت به مشکلات | استدلال قیاسی | استدلال استقرایی | روان بودن ایده‌ها | چالاکی انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | محیط‌های داخلی، کنترل‌شده از نظر دما | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | تعداد دفعات تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق بودن یا صحت بالا | صرف زمان به صورت نشسته | فشار زمانی | اهمیت تکرار کارهای مشابه</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | فشار زمانی | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های پخش رسانه‌ای | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران سیستم‌های اطلاعاتی و کامپیوتری | تعمیرکاران کامپیوتر، خودپرداز و ماشین‌های اداری | مدیران پایگاه داده | تکنسین‌ها و فن‌آوران مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصب‌کنندگان و تعمیرکاران تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | مدیران وب | طراحان رابط‌های دیجیتال و وب</t>
+          <t>تکنسین‌های پخش | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | مدیران پایگاه داده | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | مدیران وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AJAX | نرم‌افزار مدیریت دسترسی | Adobe ActionScript | Adobe After Effects | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | AirMagnet Enterprise | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | نرم‌افزار مدیریت برنامه‌ها | Aruba Networks AirWave | نرم‌افزار مدیریت دارایی‌ها | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk Revit | نرم‌افزار نصب خودکار | Bash | Blink | پروتکل مسیریابی مرزی BGP | BroadSoft BroadWorks | C | C# | C++ | CA eTrust | نرم‌افزار برنامه‌ریزی ظرفیت | برگه شیوه‌نامه آبشاری CSS | Chef | Cisco IOS | پروتکل ارتباطی کش وب سیسکو WCCP | Cisco Systems CiscoWorks | Cisco Systems CiscoWorks LAN Management Solution | پروتکل تعادل بار گیت‌وی سیسکو GLBP | پروتکل روتر آماده‌به‌کار گرم سیسکو HSRP | سیستم کنترل بی‌سیم سیسکو WCS | Cisco Webex | Citrix XenApp | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | Compaq Insight Manager | Computer Associates ArcServ Backup | سیستم‌های تشخیص نفوذ کامپیوتری | نرم‌افزار فیلتر محتوا | سیستم کنترل اطلاعات مشتری CICS | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ترسیم نمودار | نرم‌افزار شبیه‌سازی رویداد گسسته | Django | Docker | سیستم نام دامنه DNS | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Dynatrace | EMC Smarts Network Protocol Manager | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | نرم‌افزار مدیریت عناصر | نرم‌افزار مدیریت ایمیل | نرم‌افزار رمزگذاری | پروتکل مسیریابی گیت‌وی داخلی پیشرفته EIGRP | Enterprise JavaBeans | Ethereal | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار فایروال | Git | GitHub | Go | Google Android | Google Angular | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM AIX | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM Terraform | IBM WebSphere | IBM WebSphere MQ | Infoblox NetMRI | نرم‌افزار امنیت و شبکه‌سازی Infoblox | نرم‌افزار محیط توسعه یکپارچه IDE | سیستم واسط به سیستم واسط IS-IS | امنیت پروتکل اینترنت IPSEC | سیستم پیشگیری از نفوذ IPS | Ipswitch WhatsUp Gold | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | KornShell | LAMP Stack | Linux | نرم‌افزار شبکه محلی LAN | LogRhythm | نرم‌افزار پارتیشن منطقی LPAR | Lucent VitalSuite | McAfee | McAfee VirusScan | Micro Focus OpenView | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Forefront Identify Manager | Microsoft Forefront Threat Management Gateway | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Minitab | MongoDB | نرم‌افزار ترسیم گراف ترافیک چند روتری MRTG | سوئیچینگ برچسب چند پروتکلی MPLS | MySQL | Nagios | National Instruments LabVIEW | NetIQ | NetScout InfinitiStream Console | Netreo OmniCenter | نرم‌افزار تست بار و عملکرد شبکه و برنامه | نرم‌افزار تحلیل عملکرد شبکه و قطعات | نرم‌افزار ارزیابی آسیب‌پذیری شبکه و سیستم | نرم‌افزار طراحی معماری شبکه | نرم‌افزار نظارت بر در دسترس بودن شبکه | نرم‌افزار پل شبکه | نرم‌افزار مستندسازی شبکه | نرم‌افزار تشخیص نفوذ شبکه | سیستم‌های پیشگیری از نفوذ شبکه NIPS | نرم‌افزار مدل‌سازی، نقشه‌برداری و تحلیل شبکه | نرم‌افزار گزارش‌دهی شبکه | نرم‌افزار ذخیره‌سازی شبکه | نرم‌افزار نظارت و تحلیل جریان ترافیک شبکه | نرم‌افزار پروب ترافیک شبکه | نرم‌افزار بهینه‌سازی شبکه، سرور و سیستم عامل | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | OPNET APMXpert | نرم‌افزار محاسبه‌گر ترافیک آنلاین | ابتدا کوتاه‌ترین مسیر باز OSPF | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle JDBC | Oracle Java | Oracle Java Enterprise Edition EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle Solaris | Oracle WebLogic Server | PHP | نرم‌افزار تحلیل بسته | نرم‌افزار فیلتر بسته | نرم‌افزار ردیابی بسته | نرم‌افزار مدیریت وصله و به‌روزرسانی | نرم‌افزار تست نفوذ | نرم‌افزار Perforce Helix | Perl | Ping Identity | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار دسترسی از راه دور | نرم‌افزار مدیریت الزامات | نرم‌افزار ارزیابی ریسک | Riverbed Technology | نرم‌افزار تحلیل علت ریشه‌ای | Ruby | Ruby on Rails | نرم‌افزار SAP | Scala | نرم‌افزار مدیریت حوادث امنیتی | Segue SilkPerformer | Selenium | پروتکل شروع جلسه SIP | شل اسکریپت | Silver Peak | پروتکل ساده انتقال ایمیل SMTP | نرم‌افزار پروتکل ساده مدیریت شبکه SNMP | Snort | نرم‌افزار توزیع نرم‌افزار | SolarWinds | Splunk Enterprise | Spring Boot | Spring Framework | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار مدیریت ذخیره‌سازی | زبان پرس‌و‌جوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Intruder Alert | نرم‌افزار بازیابی فاجعه سیستم و داده‌ها | نرم‌افزار تست سیستم | نرم‌افزار مهاجرت سیستم‌ها و برنامه‌ها | Tableau | Tcpdump | Teradata Database | The MathWorks MATLAB | نرم‌افزار ردیابی اطلاعات تیکت | نرم‌افزار گزارش‌دهی زمان | Transact-SQL | اتصال شفاف تعداد زیادی لینک TRILL | Trimble SketchUp Pro | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Verilog | Veritas NetBackup | نرم‌افزار ویدیوکنفرانس | پروتکل افزونگی روتر مجازی VRRP | نرم‌افزار مدیریت شبکه محلی مجازی | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار اسکن ویروس | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | Websense Data Loss Prevention | نرم‌افزار بهینه‌سازی شبکه گسترده WAN | نرم‌افزار شبکه گسترده WAN | Wireshark | jQuery</t>
+          <t>AJAX | نرم‌افزار مدیریت دسترسی | Adobe ActionScript | Adobe After Effects | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | AirMagnet Enterprise | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | نرم‌افزار مدیریت برنامه‌ها | Aruba Networks AirWave | نرم‌افزار مدیریت دارایی‌ها | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | Autodesk Revit | نرم‌افزار نصب خودکار | Bash | Blink | پروتکل مسیریابی مرزی BGP | BroadSoft BroadWorks | C | C# | C++ | CA eTrust | نرم‌افزار برنامه‌ریزی ظرفیت | برگه‌های سبک آبشاری CSS | Chef | Cisco IOS | پروتکل ارتباطی کش وب سیسکو WCCP | Cisco Systems CiscoWorks | Cisco Systems CiscoWorks LAN Management Solution | پروتکل تعادل بار گیت‌وی سیسکو GLBP | پروتکل روتر آماده‌به‌کار گرم سیسکو HSRP | سیستم کنترل بی‌سیم سیسکو WCS | Cisco Webex | Citrix XenApp | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | Compaq Insight Manager | Computer Associates ArcServ Backup | سیستم‌های تشخیص نفوذ کامپیوتری | نرم‌افزار فیلتر محتوا | سیستم کنترل اطلاعات مشتری CICS | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار نمودارکشی | نرم‌افزار شبیه‌سازی رویداد گسسته | Django | Docker | سیستم نام دامنه DNS | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Dynatrace | EMC Smarts Network Protocol Manager | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | نرم‌افزار مدیریت عناصر | نرم‌افزار مدیریت ایمیل | نرم‌افزار رمزگذاری | پروتکل مسیریابی گیت‌وی داخلی پیشرفته EIGRP | Enterprise JavaBeans | Ethereal | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار فایروال | Git | GitHub | Go | Google Android | Google Angular | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM AIX | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM Terraform | IBM WebSphere | IBM WebSphere MQ | Infoblox NetMRI | نرم‌افزار امنیت و شبکه‌سازی Infoblox | نرم‌افزار محیط توسعه یکپارچه IDE | سیستم واسط به سیستم واسط IS-IS | امنیت پروتکل اینترنت IPSEC | سیستم پیشگیری از نفوذ IPS | Ipswitch WhatsUp Gold | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | KornShell | LAMP Stack | Linux | نرم‌افزار شبکه محلی LAN | LogRhythm | نرم‌افزار پارتیشن منطقی LPAR | Lucent VitalSuite | McAfee | McAfee VirusScan | Micro Focus OpenView | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Forefront Identify Manager | Microsoft Forefront Threat Management Gateway | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Minitab | MongoDB | نرم‌افزار ترسیم گراف ترافیک چند روتری MRTG | سوئیچینگ برچسب چند پروتکلی MPLS | MySQL | Nagios | National Instruments LabVIEW | NetIQ | NetScout InfinitiStream Console | Netreo OmniCenter | نرم‌افزار تست بار و عملکرد شبکه و برنامه | نرم‌افزار تحلیل عملکرد شبکه و قطعات | نرم‌افزار ارزیابی آسیب‌پذیری شبکه و سیستم | نرم‌افزار طراحی معماری شبکه | نرم‌افزار نظارت بر در دسترس بودن شبکه | نرم‌افزار پل شبکه | نرم‌افزار مستندسازی شبکه | نرم‌افزار تشخیص نفوذ شبکه | سیستم‌های پیشگیری از نفوذ شبکه NIPS | نرم‌افزار مدل‌سازی، نقشه‌برداری و تحلیل شبکه | نرم‌افزار گزارش‌دهی شبکه | نرم‌افزار ذخیره‌سازی شبکه | نرم‌افزار نظارت و تحلیل جریان ترافیک شبکه | نرم‌افزار پروب ترافیک شبکه | نرم‌افزار بهینه‌سازی شبکه، سرور و سیستم عامل | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | OPNET APMXpert | نرم‌افزار محاسبه‌گر ترافیک آنلاین | ابتدا کوتاه‌ترین مسیر باز OSPF | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle JDBC | Oracle Java | Oracle Java Enterprise Edition EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle Solaris | Oracle WebLogic Server | PHP | نرم‌افزار تحلیل بسته | نرم‌افزار فیلتر بسته | نرم‌افزار ردیابی بسته | نرم‌افزار مدیریت وصله و به‌روزرسانی | نرم‌افزار تست نفوذ | نرم‌افزار Perforce Helix | Perl | Ping Identity | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار دسترسی از راه دور | نرم‌افزار مدیریت الزامات | نرم‌افزار ارزیابی ریسک | Riverbed Technology | نرم‌افزار تحلیل علت ریشه‌ای | Ruby | Ruby on Rails | نرم‌افزار SAP | Scala | نرم‌افزار مدیریت حوادث امنیتی | Segue SilkPerformer | Selenium | پروتکل شروع جلسه SIP | Shell script | Silver Peak | پروتکل ساده انتقال ایمیل SMTP | نرم‌افزار پروتکل آسان مدیریت شبکه SNMP | Snort | نرم‌افزار توزیع نرم‌افزار | SolarWinds | Splunk Enterprise | Spring Boot | Spring Framework | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار مدیریت ذخیره‌سازی | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Intruder Alert | نرم‌افزار بازیابی فاجعه سیستم و داده‌ها | نرم‌افزار تست سیستم | نرم‌افزار مهاجرت سیستم‌ها و برنامه‌ها | Tableau | Tcpdump | Teradata Database | The MathWorks MATLAB | نرم‌افزار ردیابی اطلاعات تیکت | نرم‌افزار گزارش‌دهی زمان | Transact-SQL | اتصال شفاف تعداد زیادی لینک TRILL | Trimble SketchUp Pro | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Verilog | Veritas NetBackup | نرم‌افزار ویدئوکنفرانس | پروتکل افزونگی روتر مجازی VRRP | نرم‌افزار مدیریت شبکه محلی مجازی | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار اسکن ویروس | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | Websense Data Loss Prevention | نرم‌افزار بهینه‌سازی شبکه گسترده WAN | نرم‌افزار شبکه گسترده WAN | Wireshark | jQuery</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | پایش | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مهندسی و فناوری | مخابرات | زبان انگلیسی | آموزش و تربیت | طراحی | خدمات مشتریان و پرسنل | ریاضیات</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | مخابرات | زبان انگلیسی | آموزش و پرورش | طراحی | خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | حساسیت به مشکلات | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | روان بودن ایده‌ها | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | استدلال ریاضی | ابتکار و اصالت</t>
+          <t>درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | محیط‌های داخلی، کنترل‌شده از نظر دما | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | مکالمات تلفنی | صرف زمان به صورت نشسته | ارتباط با دیگران | اهمیت دقیق بودن یا صحت بالا | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای نشستن | ارتباط با دیگران | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | تکنسین‌های پخش رسانه‌ای | مهندسان سخت‌افزار کامپیوتر | متخصصان پشتیبانی شبکه کامپیوتری | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | تکنسین‌ها و فن‌آوران مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | تست‌کنندگان نفوذ | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات | نصب‌کنندگان و تعمیرکاران تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط</t>
+          <t>مهندسان بلاک‌چین | تکنسین‌های پخش | مهندسان سخت‌افزار کامپیوتر | متخصصان پشتیبانی شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2AB iLock Security Services | نرم‌افزار مدیریت دسترسی | نرم‌افزار آنتی‌ویروس | Apache Kafka | Autodesk AutoCAD | Autodesk Navisworks | Autodesk Revit | Avaya Identity Engines | نرم‌افزار حسابداری تماس | Cisco Systems Cisco Traffic Analyzer | نرم‌افزار فایروال | IBM Domino | IBM Lotus 1-2-3 | IBM Notes | IBM Rational Requirements Composer | KornShell | Linux | McAfee | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Nagios | NavisWorks Jetstream | نرم‌افزار مدیریت شبکه | نرم‌افزار امنیت سایبری NortonLifeLock | NovaStor NovaBACKUP | Oracle Java | Perl | نرم‌افزار زمان‌بندی پروژه | Python | نرم‌افزار تحلیل الزامات | شل اسکریپت | SiteMaster SiteSmart | زبان پرس‌و‌جوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | UNIX | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | نرم‌افزار طراحی وب | Wireshark | Zmanda Amanda</t>
+          <t>2AB iLock Security Services | نرم‌افزار مدیریت دسترسی | نرم‌افزار آنتی‌ویروس | Apache Kafka | Autodesk AutoCAD | Autodesk Navisworks | Autodesk Revit | Avaya Identity Engines | نرم‌افزار حسابداری تماس | Cisco Systems Cisco Traffic Analyzer | نرم‌افزار فایروال | IBM Domino | IBM Lotus 1-2-3 | IBM Notes | IBM Rational Requirements Composer | KornShell | Linux | McAfee | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Nagios | NavisWorks Jetstream | نرم‌افزار مدیریت شبکه | نرم‌افزار امنیت سایبری NortonLifeLock | NovaStor NovaBACKUP | Oracle Java | Perl | نرم‌افزار زمان‌بندی پروژه | Python | نرم‌افزار تحلیل الزامات | Shell script | SiteMaster SiteSmart | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | UNIX | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | نرم‌افزار طراحی وب | Wireshark | Zmanda Amanda</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | پایش | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مخابرات | مهندسی و فناوری | کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | خدمات مشتریان و پرسنل | مدیریت و سازماندهی | طراحی</t>
+          <t>مخابرات | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مشکلات | بینایی نزدیک | درک کتبی | سازماندهی اطلاعات | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ابتکار و اصالت | روان بودن ایده‌ها | وضوح گفتار | تشخیص گفتار | سهولت در کار با اعداد | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال قیاسی | استدلال استقرایی | اصالت | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | محیط‌های داخلی، کنترل‌شده از نظر دما | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | برخورد با مشتریان خارجی یا عموم مردم | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های پخش رسانه‌ای | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | مدیران پایگاه داده | تکنسین‌ها و فن‌آوران مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | نصب‌کنندگان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | توسعه‌دهندگان نرم‌افزار | نصب‌کنندگان و تعمیرکاران تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | نصب‌کنندگان و تعمیرکاران خطوط مخابراتی</t>
+          <t>تکنسین‌های پخش | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | توسعه‌دهندگان نرم‌افزار | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ADO.NET | AJAX | ASG Technologies ASG-Zeke | Ab Initio | نرم‌افزار مدیریت دسترسی | Acronis Recovery Expert | Adobe Dreamweaver | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon Data Pipeline | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Airflow | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Mahout | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Sqoop | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk Revit | BMC Software Change Manager | BMC Software Control-M | BMC Software Recovery Manager RMAN | Backbone.js | Bash | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | C | C# | C++ | CA Easytrieve Report Generator | CA IDMS | برگه شیوه‌نامه آبشاری CSS | نرم‌افزار ناوبری کاتالوگ | Chef | Cisco Webex | نرم‌افزار رایانش ابری Citrix | نرم‌افزار سرور کلاستر | زبان مشترک تجاری COBOL | Computer Associates Log Analyzer | نرم‌افزار کنترل همزمانی | Couchbase Server | سیستم کنترل اطلاعات مشتری CICS | DOS shell script | Dassault Systemes CATIA | زبان تعریف داده DDL | نرم‌افزار فرهنگ داده | زبان دستکاری داده DML | نرم‌افزار نگاشت داده | نرم‌افزار مدل‌سازی داده | نرم‌افزار خدمات انتقال داده DTS | نرم‌افزار اعتبارسنجی داده | نرم‌افزار برنامه‌ریزی ظرفیت پایگاه داده | نرم‌افزار شبیه‌سازی پایگاه داده | نرم‌افزار طراحی پایگاه داده | نرم‌افزار امنیت پایگاه داده | نرم‌افزار پایگاه داده | نرم‌افزار تست پایگاه داده | Delphi Technology | نرم‌افزار استقرار | Django | Docker | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | EMC NetWorker | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | Ellucian Banner ERP | Embarcadero Technologies DBArtisan | نرم‌افزار رمزگذاری | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | Google Meet | Greenplum Database | HP DataProtector | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM ADSTAR | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Informix | IBM Interactive System Productivity Facility ISPF | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Data Architect | IBM SPSS Statistics | IBM Terraform | IBM WebSphere | نرم‌افزار تنظیم ایندکس | Informatica Big Data | Informatica Corporation PowerCenter | نرم‌افزار Informatica | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Jupyter Notebook | KornShell | Kubernetes | LAMP Stack | LexisNexis | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | MapR Converged Data Platform | MariaDB | Marketo Marketing Automation | McAfee | Micosoft SQL Server Analysis Services SSAS | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure Data Factory | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | Nearpod | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | سیستم مدیریت پایگاه داده شیءگرا ODBMS | Oracle Application Express APEX | Oracle Business Intelligence Enterprise Edition | Oracle Data Guard | Oracle Database | Oracle Designer | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Enterprise Manager | Oracle Enterprise Manager Cloud Control | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Golden Gate | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Learning Management | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Real Application Cluster RAC | Oracle Reports | Oracle SQL Developer | Oracle SQL Loader | Oracle SQL Plus | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | Pentaho Kettle | Perforce Helix software | Perl | PostgreSQL | Prolog | Puppet | PySpark | Python | Qlik Tech QlikView | Quest Central | Quest Erwin Data Modeler | Quest SharePlex | R | ReCrystallize Crystal Reports | Red Hat Ansible Engine | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redgate SQL Server | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سیستم مدیریت پایگاه داده رابطه‌ای | مجری توسعه‌یافته ساختاریافته REXX | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Crystal Reports | SAP PowerBuilder | SAP Replication Server | نرم‌افزار SAP | SAS | Safe Software FME | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Selenium | SentryOne SQL Sentry | شل اسکریپت | Skype | Snowflake | SolarWinds | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار مدیریت ذخیره‌سازی | زبان پرس‌و‌جوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | نرم‌افزار بازیابی فاجعه سیستم‌ها و داده‌ها | Tableau | Teradata Active Enterprise Data Warehouse | Teradata Database | نرم‌افزار تولید داده‌های تست | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | Visual Paradigm DB Visual ARCHITECT | Wireshark | Zabbix | jQuery</t>
+          <t>ADO.NET | AJAX | ASG Technologies ASG-Zeke | Ab Initio | نرم‌افزار مدیریت دسترسی | Acronis Recovery Expert | Adobe Dreamweaver | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon Data Pipeline | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Airflow | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Mahout | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Sqoop | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk Revit | BMC Software Change Manager | BMC Software Control-M | BMC Software Recovery Manager RMAN | Backbone.js | Bash | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | C | C# | C++ | CA Easytrieve Report Generator | CA IDMS | برگه‌های سبک آبشاری CSS | نرم‌افزار ناوبری کاتالوگ | Chef | Cisco Webex | نرم‌افزار رایانش ابری Citrix | نرم‌افزار سرور کلاستر | زبان مشترک تجاری COBOL | Computer Associates Log Analyzer | نرم‌افزار کنترل همزمانی | Couchbase Server | سیستم کنترل اطلاعات مشتری CICS | DOS shell script | Dassault Systemes CATIA | زبان تعریف داده DDL | نرم‌افزار فرهنگ داده | زبان دستکاری داده DML | نرم‌افزار نگاشت داده | نرم‌افزار مدل‌سازی داده | نرم‌افزار خدمات انتقال داده DTS | نرم‌افزار اعتبارسنجی داده | نرم‌افزار برنامه‌ریزی ظرفیت پایگاه داده | نرم‌افزار شبیه‌سازی پایگاه داده | نرم‌افزار طراحی پایگاه داده | نرم‌افزار امنیت پایگاه داده | نرم‌افزار پایگاه داده | نرم‌افزار تست پایگاه داده | Delphi Technology | نرم‌افزار استقرار | Django | Docker | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | EMC NetWorker | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | Ellucian Banner ERP | Embarcadero Technologies DBArtisan | نرم‌افزار رمزگذاری | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | Google Meet | Greenplum Database | HP DataProtector | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM ADSTAR | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Informix | IBM Interactive System Productivity Facility ISPF | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Data Architect | IBM SPSS Statistics | IBM Terraform | IBM WebSphere | نرم‌افزار تنظیم ایندکس | Informatica Big Data | Informatica Corporation PowerCenter | نرم‌افزار Informatica | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Jupyter Notebook | KornShell | Kubernetes | LAMP Stack | LexisNexis | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | MapR Converged Data Platform | MariaDB | Marketo Marketing Automation | McAfee | Micosoft SQL Server Analysis Services SSAS | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure Data Factory | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | Nearpod | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | سیستم مدیریت پایگاه داده شیءگرا ODBMS | Oracle Application Express APEX | Oracle Business Intelligence Enterprise Edition | Oracle Data Guard | Oracle Database | Oracle Designer | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Enterprise Manager | Oracle Enterprise Manager Cloud Control | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Golden Gate | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Learning Management | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Real Application Cluster RAC | Oracle Reports | Oracle SQL Developer | Oracle SQL Loader | Oracle SQL Plus | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | Pentaho Kettle | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Prolog | Puppet | PySpark | Python | Qlik Tech QlikView | Quest Central | Quest Erwin Data Modeler | Quest SharePlex | R | ReCrystallize Crystal Reports | Red Hat Ansible Engine | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redgate SQL Server | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سیستم مدیریت پایگاه داده رابطه‌ای | مجری توسعه‌یافته بازسازی‌شده REXX | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Crystal Reports | SAP PowerBuilder | SAP Replication Server | نرم‌افزار SAP | SAS | Safe Software FME | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Selenium | SentryOne SQL Sentry | Shell script | Skype | Snowflake | SolarWinds | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار مدیریت ذخیره‌سازی | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | نرم‌افزار بازیابی فاجعه سیستم‌ها و داده‌ها | Tableau | Teradata Active Enterprise Data Warehouse | Teradata Database | نرم‌افزار تولید داده‌های تست | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | Visual Paradigm DB Visual ARCHITECT | Wireshark | Zabbix | jQuery</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | پایش | نگارش | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | خدمات مشتریان و پرسنل | ریاضیات | مخابرات | مهندسی و فناوری | مدیریت و سازماندهی | آموزش و تربیت</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | مخابرات | مهندسی و فناوری | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مشکلات | استدلال استقرایی | سازماندهی اطلاعات | درک شفاهی | درک کتبی | بینایی نزدیک | بیان شفاهی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | روان بودن ایده‌ها | ابتکار و اصالت | توجه انتخابی | تجسم فضایی | سرعت ادراکی | سهولت در کار با اعداد</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بینایی نزدیک | بیان شفاهی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | روانی ایده‌ها | اصالت | توجه انتخابی | تجسم | سرعت ادراکی | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | محیط‌های داخلی، کنترل‌شده از نظر دما | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق بودن یا صحت بالا | صرف زمان به صورت نشسته | تعیین وظایف, اولویت‌ها و اهداف | ارتباط با دیگران | تعداد دفعات تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | متخصصان انبارش داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | تست‌کنندگان نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان رابط‌های دیجیتال و وب</t>
+          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | متخصصان انبارش داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3M Post-it App | ADO.NET | AJAX | ASG Technologies ASG-Zeke | Ab Initio | نرم‌افزار مدیریت دسترسی | Acronis Recovery Expert | Adeptia ETL Suite | Adobe Acrobat | Adobe Dreamweaver | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Altova MapForce | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Airflow | Apache Ant | Apache Avro | Apache Cassandra | Apache Flume | Apache Groovy | Apache HBase | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Mahout | Apache Maven | Apache Oozie | Apache Pig | Apache Solr | Apache Spark | Apache Sqoop | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apatar | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk Revit | BMC Software Change Manager | BMC Software Control-M | BMC Software Recovery Manager RMAN | Backbone.js | Bash | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | C | C shell | C# | C++ | CA Easytrieve Report Generator | CA IDMS | CA Technologies ERWin Data Modeler | برگه شیوه‌نامه آبشاری CSS | نرم‌افزار ناوبری کاتالوگ | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Cloudera Impala | CloverETL | نرم‌افزار سرور کلاستر | Coglin Mill RODIN | زبان مشترک تجاری COBOL | Computer Associates Log Analyzer | نرم‌افزار کنترل همزمانی | Couchbase Server | سیستم کنترل اطلاعات مشتری CICS | DOS shell script | Data Recovery Software SQL Server Data Recovery | زبان تعریف داده DDL | نرم‌افزار فرهنگ داده | زبان دستکاری داده DML | نرم‌افزار نگاشت داده | نرم‌افزار مدل‌سازی داده | نرم‌افزار خدمات انتقال داده DTS | نرم‌افزار اعتبارسنجی داده | نرم‌افزار برنامه‌ریزی ظرفیت پایگاه داده | نرم‌افزار شبیه‌سازی پایگاه داده | نرم‌افزار طراحی پایگاه داده | سیستم‌های مدیریت پایگاه داده | نرم‌افزار امنیت پایگاه داده | نرم‌افزار تست پایگاه داده | نرم‌افزار استقرار | Django | Docker | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | EMC NetWorker | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | Ellucian Banner ERP | Embarcadero Technologies DBArtisan | نرم‌افزار رمزگذاری | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | Flat File Checker | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | Google Docs | Google Drive | Google Meet | Google Sites | Greenplum Database | HP DataProtector | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | HiT Software Allora | Hibernate ORM | زبان نشانه‌گذاری ابرمتن HTML | IBM ADSTAR | IBM AIX | IBM Cognos Impromptu | IBM Content Manager | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM InfoSphere Warehouse | IBM Informix | IBM Interactive System Productivity Facility ISPF | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Data Architect | IBM Rational System Architect | IBM SPSS Statistics | IBM WebSphere | نرم‌افزار تنظیم ایندکس | Infobright Community Edition ICE | Informatica Big Data | Informatica Corporation PowerCenter | Informatica PowerCenter | نرم‌افزار Informatica | نرم‌افزار محیط توسعه یکپارچه IDE | Intel Data Migration Software | Interface Computers Data Loader | JUnit | JavaScript | JavaScript Object Notation JSON | Jitterbit | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LAMP Stack | LexisNexis | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | MapR Converged Data Platform | MariaDB | McAfee | Micosoft SQL Server Analysis Services SSAS | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Minitab | MongoDB | عبارات چند بعدی MDX | MySQL | Nagios | Nearpod | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | سیستم مدیریت پایگاه داده شیءگرا ODBMS | Oracle Application Express APEX | Oracle Application Server | Oracle Business Intelligence Enterprise Edition | Oracle Data Guard | Oracle Data Integrator | Oracle Database | Oracle Designer | Oracle Eloqua | Oracle Enterprise Manager | Oracle Enterprise Manager Cloud Control | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Golden Gate | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Jdeveloper | Oracle Migration Workbench | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Real Application Cluster RAC | Oracle Recovery Manager | Oracle Reports | Oracle SQL Developer | Oracle SQL Loader | Oracle SQL Plus | Oracle Solaris | Oracle WebLogic Server | PHP | Pentaho Kettle | Perforce Helix software | Perl | Perl shell | PostgreSQL | Prolog | Puppet | Python | Qlik Tech QlikView | Quest Central | Quest Erwin Data Modeler | Quest SQL Optimizer for Oracle | Quest SharePlex | R | Rapid-I RapidMiner | ReCrystallize Crystal Reports | React | Red Hat Ansible Engine | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redgate SQL Server | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سیستم مدیریت پایگاه داده رابطه‌ای | مجری توسعه‌یافته ساختاریافته REXX | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Crystal Reports | SAP PowerBuilder | SAP PowerDesigner | SAP Replication Server | نرم‌افزار SAP | SAS | SAS Data Integration Studio | SMSi Twister Data Integrator | Safe Software FME | نرم‌افزار Salesforce | Scala | Scriptella | Selenium | SentryOne SQL Sentry | شل اسکریپت | Skype | Snowflake | SolarWinds | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار مدیریت ذخیره‌سازی | زبان پرس‌و‌جوی ساختاریافته SQL | Swift | نرم‌افزار بازیابی فاجعه سیستم‌ها و داده‌ها | Tableau | Talend Big Data Integration | Talend Data Fabric | Talend Open Studio | Teradata Active Enterprise Data Warehouse | Teradata Database | نرم‌افزار تولید داده‌های تست | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | Visual Paradigm DB Visual ARCHITECT | Wireshark | WisdomForce DatabaseSync System | Zabbix | jQuery</t>
+          <t>3M Post-it App | ADO.NET | AJAX | ASG Technologies ASG-Zeke | Ab Initio | نرم‌افزار مدیریت دسترسی | Acronis Recovery Expert | Adeptia ETL Suite | Adobe Acrobat | Adobe Dreamweaver | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Altova MapForce | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Airflow | Apache Ant | Apache Avro | Apache Cassandra | Apache Flume | Apache Groovy | Apache HBase | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Mahout | Apache Maven | Apache Oozie | Apache Pig | Apache Solr | Apache Spark | Apache Sqoop | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apatar | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk Revit | BMC Software Change Manager | BMC Software Control-M | BMC Software Recovery Manager RMAN | Backbone.js | Bash | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | C | C shell | C# | C++ | CA Easytrieve Report Generator | CA IDMS | CA Technologies ERWin Data Modeler | برگه‌های سبک آبشاری CSS | نرم‌افزار ناوبری کاتالوگ | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Cloudera Impala | CloverETL | نرم‌افزار سرور کلاستر | Coglin Mill RODIN | زبان مشترک تجاری COBOL | Computer Associates Log Analyzer | نرم‌افزار کنترل همزمانی | Couchbase Server | سیستم کنترل اطلاعات مشتری CICS | DOS shell script | Data Recovery Software SQL Server Data Recovery | زبان تعریف داده DDL | نرم‌افزار فرهنگ داده | زبان دستکاری داده DML | نرم‌افزار نگاشت داده | نرم‌افزار مدل‌سازی داده | نرم‌افزار خدمات انتقال داده DTS | نرم‌افزار اعتبارسنجی داده | نرم‌افزار برنامه‌ریزی ظرفیت پایگاه داده | نرم‌افزار شبیه‌سازی پایگاه داده | نرم‌افزار طراحی پایگاه داده | سیستم‌های مدیریت پایگاه داده | نرم‌افزار امنیت پایگاه داده | نرم‌افزار تست پایگاه داده | نرم‌افزار استقرار | Django | Docker | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | EMC NetWorker | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | Ellucian Banner ERP | Embarcadero Technologies DBArtisan | نرم‌افزار رمزگذاری | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | Flat File Checker | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | Google Docs | Google Drive | Google Meet | Google Sites | Greenplum Database | HP DataProtector | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | HiT Software Allora | Hibernate ORM | زبان نشانه‌گذاری ابرمتن HTML | IBM ADSTAR | IBM AIX | IBM Cognos Impromptu | IBM Content Manager | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM InfoSphere Warehouse | IBM Informix | IBM Interactive System Productivity Facility ISPF | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Data Architect | IBM Rational System Architect | IBM SPSS Statistics | IBM WebSphere | نرم‌افزار تنظیم ایندکس | Infobright Community Edition ICE | Informatica Big Data | Informatica Corporation PowerCenter | Informatica PowerCenter | نرم‌افزار Informatica | نرم‌افزار محیط توسعه یکپارچه IDE | Intel Data Migration Software | Interface Computers Data Loader | JUnit | JavaScript | JavaScript Object Notation JSON | Jitterbit | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LAMP Stack | LexisNexis | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | MapR Converged Data Platform | MariaDB | McAfee | Micosoft SQL Server Analysis Services SSAS | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Minitab | MongoDB | عبارات چند بعدی MDX | MySQL | Nagios | Nearpod | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | سیستم مدیریت پایگاه داده شیءگرا ODBMS | Oracle Application Express APEX | Oracle Application Server | Oracle Business Intelligence Enterprise Edition | Oracle Data Guard | Oracle Data Integrator | Oracle Database | Oracle Designer | Oracle Eloqua | Oracle Enterprise Manager | Oracle Enterprise Manager Cloud Control | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Golden Gate | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Jdeveloper | Oracle Migration Workbench | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Real Application Cluster RAC | Oracle Recovery Manager | Oracle Reports | Oracle SQL Developer | Oracle SQL Loader | Oracle SQL Plus | Oracle Solaris | Oracle WebLogic Server | PHP | Pentaho Kettle | نرم‌افزار Perforce Helix | Perl | Perl shell | PostgreSQL | Prolog | Puppet | Python | Qlik Tech QlikView | Quest Central | Quest Erwin Data Modeler | Quest SQL Optimizer for Oracle | Quest SharePlex | R | Rapid-I RapidMiner | ReCrystallize Crystal Reports | React | Red Hat Ansible Engine | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redgate SQL Server | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سیستم مدیریت پایگاه داده رابطه‌ای | مجری توسعه‌یافته بازسازی‌شده REXX | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Crystal Reports | SAP PowerBuilder | SAP PowerDesigner | SAP Replication Server | نرم‌افزار SAP | SAS | SAS Data Integration Studio | SMSi Twister Data Integrator | Safe Software FME | نرم‌افزار Salesforce | Scala | Scriptella | Selenium | SentryOne SQL Sentry | Shell script | Skype | Snowflake | SolarWinds | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار مدیریت ذخیره‌سازی | زبان پرس‌وجوی ساختاریافته SQL | Swift | نرم‌افزار بازیابی فاجعه سیستم‌ها و داده‌ها | Tableau | Talend Big Data Integration | Talend Data Fabric | Talend Open Studio | Teradata Active Enterprise Data Warehouse | Teradata Database | نرم‌افزار تولید داده‌های تست | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | Visual Paradigm DB Visual ARCHITECT | Wireshark | WisdomForce DatabaseSync System | Zabbix | jQuery</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | پایش | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مهندسی و فناوری | طراحی | ریاضیات | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | طراحی | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مشکلات | استدلال استقرایی | سازماندهی اطلاعات | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | بیان کتبی | روان بودن ایده‌ها | انعطاف‌پذیری بستار | توجه انتخابی | سهولت در کار با اعداد | استدلال ریاضی | سرعت ادراکی | تشخیص گفتار | ابتکار و اصالت</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | بیان کتبی | روانی ایده‌ها | انعطاف‌پذیری بستار | توجه انتخابی | توانایی عددی | استدلال ریاضی | سرعت ادراکی | تشخیص گفتار | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | اهمیت دقیق بودن یا صحت بالا | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط‌های داخلی، کنترل‌شده از نظر دما | تعیین وظایف، اولویت‌ها و اهداف | میزان رقابت | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | تحلیل‌گران هوش تجاری | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران سیستم‌های اطلاعاتی و کامپیوتری | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | متخصصان مدیریت اسناد | تکنسین‌ها و فن‌آوران سیستم‌های اطلاعات جغرافیایی | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران تحقیق در عملیات | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | طراحان رابط‌های دیجیتال و وب</t>
+          <t>مهندسان بلاک‌چین | تحلیلگران هوش تجاری | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | متخصصان مدیریت اسناد | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران تحقیق در عملیات | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adaptive Metadata Manager | Adeptia ETL Suite | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Altova MapForce | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | نرم‌افزار Amazon Web Services AWS | Apache Avro | Apache Cassandra | Apache Flume | Apache HBase | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Oozie | Apache Pig | Apache Solr | Apache Spark | Apache Sqoop | Apache Subversion SVN | Apatar | Apple macOS | Aster Data nCluster | Atlassian JIRA | Bash | Blackbaud The Raiser's Edge | C | C# | C++ | Cloudera Impala | CloverETL | CodeFutures dbShards | Coglin Mill RODIN | زبان مشترک تجاری COBOL | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Embarcadero ER/Studio XE | زبان نشانه‌گذاری توسعه‌پذیر XML | Flat File Checker | Greenplum Database | Hewlett Packard HP-UX | HiT Software Allora | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Clarity Systems Clarity | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Netezza TwinFin | IBM SPSS Statistics | IBM WebSphere | Informatica PowerCenter | نرم‌افزار Informatica | نرم‌افزار محیط توسعه یکپارچه IDE | InterMine | Jitterbit | زبان کنترل کار JCL | Kalido Information Engine | KornShell | Linux | McAfee | MicroStrategy | Microsoft .NET Framework | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | MongoDB | MySQL | Nagios | NetSuite ERP | NoSQL | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | نرم‌افزار ذخیره داده‌های عملیاتی ODS | Oracle Business Intelligence Discoverer | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle Java | Oracle PL/SQL | Oracle PeopleSoft | Oracle SQL Loader | Oracle Solaris | Oracle Warehouse Builder | Oracle WebLogic Server | ParAccel Analytic Database | Pentaho Kettle | Perforce Helix software | Perl | PostgreSQL | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Rapid-I RapidMiner | Red Hat Enterprise Linux | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby on Rails | SAND | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Crystal Reports | SAP IQ | SAP NetWeaver BW | SAP PowerDesigner | نرم‌افزار SAP | SAS | SAS Data Integration Server | SMSi Twister Data Integrator | Scala | Scriptella | شل اسکریپت | Splunk Enterprise | StataCorp Stata | زبان پرس‌و‌جوی ساختاریافته SQL | TIBCO Spotfire | Tableau | Talend Big Data Integration | Talend Data Fabric | Talend Open Studio | TalendForge | Teradata BTEQ | Teradata Database | Teradata FastExport | Teradata FastLoad | Teradata Parallel Transporter | Teradata Tpump | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | WisdomForce DatabaseSync System</t>
+          <t>Adaptive Metadata Manager | Adeptia ETL Suite | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Altova MapForce | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | نرم‌افزار Amazon Web Services AWS | Apache Avro | Apache Cassandra | Apache Flume | Apache HBase | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Oozie | Apache Pig | Apache Solr | Apache Spark | Apache Sqoop | Apache Subversion SVN | Apatar | Apple macOS | Aster Data nCluster | Atlassian JIRA | Bash | Blackbaud The Raiser's Edge | C | C# | C++ | Cloudera Impala | CloverETL | CodeFutures dbShards | Coglin Mill RODIN | زبان مشترک تجاری COBOL | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Embarcadero ER/Studio XE | زبان نشانه‌گذاری توسعه‌پذیر XML | Flat File Checker | Greenplum Database | Hewlett Packard HP-UX | HiT Software Allora | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Clarity Systems Clarity | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Netezza TwinFin | IBM SPSS Statistics | IBM WebSphere | Informatica PowerCenter | نرم‌افزار Informatica | نرم‌افزار محیط توسعه یکپارچه IDE | InterMine | Jitterbit | زبان کنترل کار JCL | Kalido Information Engine | KornShell | Linux | McAfee | MicroStrategy | Microsoft .NET Framework | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | MongoDB | MySQL | Nagios | NetSuite ERP | NoSQL | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | Oracle Business Intelligence Discoverer | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle Java | Oracle PL/SQL | Oracle PeopleSoft | Oracle SQL Loader | Oracle Solaris | Oracle Warehouse Builder | Oracle WebLogic Server | ParAccel Analytic Database | Pentaho Kettle | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Rapid-I RapidMiner | Red Hat Enterprise Linux | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Ruby on Rails | SAND | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Crystal Reports | SAP IQ | SAP NetWeaver BW | SAP PowerDesigner | نرم‌افزار SAP | SAS | SAS Data Integration Server | SMSi Twister Data Integrator | Scala | Scriptella | Shell script | Splunk Enterprise | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | TIBCO Spotfire | Tableau | Talend Big Data Integration | Talend Data Fabric | Talend Open Studio | TalendForge | Teradata BTEQ | Teradata Database | Teradata FastExport | Teradata FastLoad | Teradata Parallel Transporter | Teradata Tpump | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Veritas NetBackup | WisdomForce DatabaseSync System</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ریاضیات | زبان انگلیسی | طراحی</t>
+          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | طراحی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | سازماندهی اطلاعات | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بیان شفاهی | حساسیت به مشکلات | وضوح گفتار | استدلال ریاضی | روان بودن ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | سهولت در کار با اعداد | ابتکار و اصالت</t>
+          <t>درک کتبی | ترتیب‌دهی اطلاعات | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | توانایی عددی | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | محیط‌های داخلی، کنترل‌شده از نظر دما | بحث‌های چهره‌به‌چهره با افراد و در تیم‌ها | اهمیت دقیق بودن یا صحت بالا | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>ایمیل | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | تحلیل‌گران هوش تجاری | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران سیستم‌های اطلاعاتی و کامپیوتری | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | مهندسان صنایع | مهندسان لجستیک | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران تحقیق در عملیات | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی | توسعه‌دهندگان وب</t>
+          <t>مهندسان بلاک‌چین | تحلیلگران هوش تجاری | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | مهندسان صنایع | مهندسان لجستیک | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران تحقیق در عملیات | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0012_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0012_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | پزشکی و دندان‌پزشکی | آموزش و پرورش | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ریاضیات | طراحی | روان‌شناسی | مهندسی و فناوری | امور اداری و دفتری | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | پزشکی و دندان‌پزشکی | آموزش و پرورش | خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | طراحی | روان‌شناسی | مهندسی و فناوری | اداری | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | بیان کتبی | ابتکار و اصالت | درک شفاهی | روان بودن ایده‌ها | وضوح گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری بستن | توجه انتخابی | سرعت ادراک</t>
+          <t>درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان شفاهی | بیان کتبی | اصالت | درک شفاهی | روانی ایده‌ها | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | پرستاران بالینی پیشرفته روان‌پزشکی | مدیران داده‌های بالینی | پرستاران بالینی متخصص | هماهنگ‌کنندگان پژوهش‌های بالینی | تحلیل‌گران سیستم‌های رایانه‌ای | پرستاران بخش مراقبت‌های ویژه | اپیدمیولوژیست‌ها | متخصصان آموزش سلامت | متخصصان فناوری اطلاعات سلامت و ثبّات‌های پزشکی | مدرسان تخصصی علوم بهداشت، آموزش عالی | بهیاران و کمک‌پرستاران دارای مجوز | متخصصان مدارک و اسناد پزشکی | مدیران خدمات درمانی و بهداشتی | پرستاران بالینی پیگیر درمان | مربیان و مدرسان پرستاری، آموزش عالی | نمایندگان حقوق بیمار | پزشکان طب پیشگیری | پرستاران دارای پروانه | دستیاران پژوهشی علوم اجتماعی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | مدیران داده‌های بالینی | پرستاران متخصص بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | پرستاران مراقبت‌های ویژه | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | کارشناسان آموزش بهداشت و ارتقای سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | بهیاران و کمک‌پرستاران دارای مجوز | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | مدیران خدمات درمانی و بهداشتی | پرستاران بالینی پیشرفته | مربیان و استادان پرستاری دانشگاه | کارشناسان امور بیماران و پذیرش | متخصصان پزشکی اجتماعی و طب پیشگیری | پرستاران | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | مدیریت و امور اداری | مخابرات | مهندسی و فناوری | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | آموزش و پرورش</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | مدیریت و اداره | مخابرات | مهندسی و فناوری | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری بستن | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراک | ابتکار و اصالت | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران سیستم‌های اطلاعاتی و فناوری | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران جرم‌یابی دیجیتال | متخصصان مدیریت اسناد | مهندسان امنیت اطلاعات | تحلیل‌گران اطلاعاتی و امنیتی | مدیران شبکه و سیستم‌های رایانه‌ای | متخصصان ارزیابی نفوذپذیری | کارشناسان مدیریت امنیت | مدیران امنیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات</t>
+          <t>مهندسان زنجیره بلوکی | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | کارشناسان مدیریت اسناد و مدارک | مهندسان امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | علوم پایه | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و امور اداری | طراحی | مخابرات</t>
+          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره | طراحی | مخابرات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | روان بودن ایده‌ها | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | ابتکار و اصالت | استدلال ریاضی | وضوح گفتار | سهولت در کار با اعداد | تجسم فضایی | تشخیص گفتار | سرعت ادراک | انعطاف‌پذیری بستن</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | بیان شفاهی | درک کتبی | روانی ایده‌ها | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | اصالت | استدلال ریاضی | وضوح گفتار | توانایی عددی | تجسم | تشخیص گفتار | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مهندسان زیستی و پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مهندسان سخت‌افزار رایانه | برنامه‌نویسان رایانه | مدرسان علوم رایانه، آموزش عالی | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های اطلاعاتی و فناوری | دانشمندان داده | معماران پایگاه داده | مدیران پروژه‌های فناوری اطلاعات | ریاضیدانان | فناوران و تکنسین‌های مهندسی نانوفناوری | مدیران علوم پایه و طبیعی | تحلیل‌گران تحقیق در عملیات | مهندسان رباتیک | توسعه‌دهندگان نرم‌افزار | آمارشناسان</t>
+          <t>مدیران فنی و مهندسی و معماری | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مهندسان سخت‌افزار رایانه | برنامه‌نویسان کامپیوتر | استادان علوم رایانه، آموزش عالی | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | دانشمندان داده | معماران پایگاه داده | مدیران پروژه‌های فناوری اطلاعات | ریاضی‌دانان | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی و پایه‌ای | تحلیل‌گران تحقیق در عملیات | مهندسان رباتیک | توسعه‌دهندگان نرم‌افزار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مخابرات | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | مخابرات | خدمات مشتری و شخصی | مهندسی و فناوری | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | درک کتبی | مرتب‌سازی اطلاعات | بیان کتبی | وضوح گفتار | تشخیص گفتار | دید نزدیک | توجه انتخابی | چابکی انگشتان | انعطاف‌پذیری بستن | انعطاف‌پذیری در طبقه‌بندی | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات | بیان کتبی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | مهارت انگشتان | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | تکنسین‌های پخش و رسانه | معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران سیستم‌های اطلاعاتی و فناوری | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکترونیکی تجاری و صنعتی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | متخصصان ارزیابی نفوذپذیری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی | مدیران وب</t>
+          <t>مهندسان زنجیره بلوکی | تکنسین‌های پخش و اتاق فرمان | معماران شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | مدیران وب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مخابرات | زبان انگلیسی | آموزش و پرورش | مکانیک | مهندسی و فناوری | مدیریت و امور اداری | امور اداری و دفتری | ارتباطات و رسانه | طراحی</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مخابرات | زبان انگلیسی | آموزش و پرورش | مکانیک | مهندسی و فناوری | مدیریت و اداره | اداری | ارتباطات و رسانه | طراحی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روان بودن ایده‌ها | چابکی انگشتان | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های پخش و رسانه | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های اطلاعاتی و فناوری | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | مدیران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکترونیکی تجاری و صنعتی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی | مدیران وب | طراحان وب و رابط کاربری دیجیتال</t>
+          <t>تکنسین‌های پخش و اتاق فرمان | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | مدیران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | مدیران وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مهندسی و فناوری | مخابرات | زبان انگلیسی | آموزش و پرورش | طراحی | خدمات مشتریان و خدمات فردی | ریاضیات</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | مخابرات | زبان انگلیسی | آموزش و پرورش | طراحی | خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | تشخیص گفتار | روان بودن ایده‌ها | انعطاف‌پذیری بستن | توجه انتخابی | سرعت ادراک | استدلال ریاضی | ابتکار و اصالت</t>
+          <t>درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | توجه انتخابی | سرعت ادراکی | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | تکنسین‌های پخش و رسانه | مهندسان سخت‌افزار رایانه | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران سیستم‌های اطلاعاتی و فناوری | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز رایانه | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | متخصصان ارزیابی نفوذپذیری | متخصصان سامانه‌های شناسایی با امواج رادیویی (RFID) | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی</t>
+          <t>مهندسان زنجیره بلوکی | تکنسین‌های پخش و اتاق فرمان | مهندسان سخت‌افزار رایانه | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | متخصصان سامانه‌های شناسایی با امواج رادیویی | توسعه‌دهندگان نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | نظارت | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | سخن گفتن | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مخابرات | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | طراحی</t>
+          <t>مخابرات | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ابتکار و اصالت | روان بودن ایده‌ها | وضوح گفتار | تشخیص گفتار | سهولت در کار با اعداد | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | دید دور | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستن</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال قیاسی | استدلال استقرایی | اصالت | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | بینایی دور | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های پخش و رسانه | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران سیستم‌های اطلاعاتی و فناوری | مدیران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکترونیکی تجاری و صنعتی | مهندسان الکترونیک، به‌جز رایانه | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | متخصصان سامانه‌های شناسایی با امواج رادیویی (RFID) | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل‌های مخابراتی | توسعه‌دهندگان نرم‌افزار | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی | نصابان و تعمیرکاران خطوط مخابراتی</t>
+          <t>تکنسین‌های پخش و اتاق فرمان | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان الکترونیک، به‌جز کامپیوتر | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان سامانه‌های شناسایی با امواج رادیویی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | توسعه‌دهندگان نرم‌افزار | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و کابل‌کشان خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | مخابرات | مهندسی و فناوری | مدیریت و امور اداری | آموزش و پرورش</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | مخابرات | مهندسی و فناوری | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | دید نزدیک | بیان شفاهی | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری بستن | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | روان بودن ایده‌ها | ابتکار و اصالت | توجه انتخابی | تجسم فضایی | سرعت ادراک | سهولت در کار با اعداد</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بینایی نزدیک | بیان شفاهی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | روانی ایده‌ها | اصالت | توجه انتخابی | تجسم | سرعت ادراکی | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران سیستم‌های اطلاعاتی و فناوری | متخصصان انباره داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | متخصصان ارزیابی نفوذپذیری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط کاربری دیجیتال</t>
+          <t>مهندسان زنجیره بلوکی | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | متخصصان انباره داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | وضوح گفتار | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | بیان کتبی | روان بودن ایده‌ها | انعطاف‌پذیری بستن | توجه انتخابی | سهولت در کار با اعداد | استدلال ریاضی | سرعت ادراک | تشخیص گفتار | ابتکار و اصالت</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | بیان کتبی | روانی ایده‌ها | انعطاف‌پذیری بستار | توجه انتخابی | توانایی عددی | استدلال ریاضی | سرعت ادراکی | تشخیص گفتار | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>مکاتبهٔ ایمیلی | نشستن طولانی‌مدت پشت میز | ارتباط تلفنی | گفت‌وگوی حضوری با همکاران | اهمیت بالای دقت در کار | استقلال و آزادی عمل در تصمیم‌گیری | کار گروهی و تیمی</t>
+          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | تحلیل‌گران هوش تجاری | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های اطلاعاتی و فناوری | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | متخصصان مدیریت اسناد | کارشناسان و تکنسین‌های سامانه‌های اطلاعات جغرافیایی (GIS) | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های رایانه‌ای | تحلیل‌گران تحقیق در عملیات | متخصصان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | طراحان وب و رابط کاربری دیجیتال</t>
+          <t>مهندسان زنجیره بلوکی | تحلیل‌گران هوش تجاری | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران تحقیق در عملیات | کارشناسان مدیریت پروژه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | مرتب‌سازی اطلاعات | درک شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال ریاضی | روان بودن ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستن | سهولت در کار با اعداد | ابتکار و اصالت</t>
+          <t>درک کتبی | ترتیب‌دهی اطلاعات | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | وضوح گفتار | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری بستار | توانایی عددی | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | تحلیل‌گران هوش تجاری | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های اطلاعاتی و فناوری | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | مهندسان صنایع | مهندسان لجستیک | مدیران شبکه و سیستم‌های رایانه‌ای | تحلیل‌گران تحقیق در عملیات | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی | توسعه‌دهندگان وب</t>
+          <t>مهندسان زنجیره بلوکی | تحلیل‌گران هوش تجاری | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | مدیران شبکه و سیستم‌های کامپیوتری | تحلیل‌گران تحقیق در عملیات | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
